--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>3.13</v>
       </c>
       <c r="N9" t="n">
-        <v>2.14</v>
+        <v>2.08</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1537,10 +1537,10 @@
         <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI9"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46009.41666666666</v>
+        <v>46009.40625</v>
       </c>
     </row>
     <row r="4">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,76 +1135,76 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46009.52083333334</v>
+        <v>46009.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,12 +1213,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46009.66666666666</v>
+        <v>46009.45486111111</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,13 +1373,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46009.66666666666</v>
+        <v>46009.47569444445</v>
       </c>
     </row>
     <row r="9">
@@ -1451,116 +1451,711 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Saham</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Al Shabab</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
+        <v>46009.51041666666</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Oman Professional League</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Al-Nahda</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Sohar</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
+        <v>46009.51041666666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Azerbaijan Premyer Liqası</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Sabah</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Qarabağ</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L11" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O11" t="n">
+        <v>5</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AI11" s="3" t="n">
+        <v>46009.52083333334</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Belgium First Division B</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Patro Eisden</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>AS Eupen</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="3" t="n">
+        <v>46009.66666666666</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Belgium First Division B</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RFC Liege</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lokeren-Temse</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="3" t="n">
+        <v>46009.66666666666</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>England EFL League One</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>Reading</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Luton Town</t>
         </is>
       </c>
-      <c r="G9" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr">
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L9" t="n">
+      <c r="L14" t="n">
         <v>3.13</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M14" t="n">
         <v>3.13</v>
       </c>
-      <c r="N9" t="n">
+      <c r="N14" t="n">
         <v>2.08</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.97</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AB14" t="n">
         <v>1.73</v>
       </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G5" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.75</v>
+        <v>4.51</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="O11" t="n">
-        <v>5</v>
+        <v>5.21</v>
       </c>
       <c r="P11" t="n">
-        <v>2.11</v>
+        <v>2.25</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
         <v>6.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
         <v>3.4</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.85</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
         <v>1.75</v>
       </c>
       <c r="AF11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.21</v>
-      </c>
       <c r="AH11" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.52083333334</v>
@@ -2096,40 +2096,40 @@
         <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="AA14" t="n">
         <v>1.97</v>
@@ -2138,22 +2138,22 @@
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G10" t="n">

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.25</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.89</v>
+        <v>1.73</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2099,7 +2099,7 @@
         <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q14" t="n">
         <v>3.19</v>
@@ -2108,13 +2108,13 @@
         <v>1.38</v>
       </c>
       <c r="S14" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
         <v>2.85</v>
       </c>
       <c r="U14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V14" t="n">
         <v>7.4</v>
@@ -2123,13 +2123,13 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.46</v>
+        <v>3.4</v>
       </c>
       <c r="AA14" t="n">
         <v>1.97</v>
@@ -2144,7 +2144,7 @@
         <v>1.26</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -856,12 +856,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Sur</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Al Seeb</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -966,7 +966,7 @@
         <v>0</v>
       </c>
       <c r="AI4" s="3" t="n">
-        <v>46009.41666666666</v>
+        <v>46009.45486111111</v>
       </c>
     </row>
     <row r="5">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Al Nasr</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oman Club</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46009.41666666666</v>
+        <v>46009.47569444445</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46009.41666666666</v>
+        <v>46009.51041666666</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Sur</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Seeb</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
-        <v>46009.45486111111</v>
+        <v>46009.51041666666</v>
       </c>
     </row>
     <row r="8">
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Nasr</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Oman Club</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,76 +1373,76 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46009.47569444445</v>
+        <v>46009.52083333334</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46009.51041666666</v>
+        <v>46009.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46009.51041666666</v>
+        <v>46009.54166666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.51</v>
+        <v>1.92</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>5.21</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.3</v>
+        <v>5.2</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.2</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46009.52083333334</v>
+        <v>46009.66666666666</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.5</v>
       </c>
-      <c r="O13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.2</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB13" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
         <v>3.5</v>
       </c>
-      <c r="O11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.2</v>
-      </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AA11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB11" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>1.56</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
         <v>2.25</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N13" t="n">
-        <v>3</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.58</v>
-      </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>5.2</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.73</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AC13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF13" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.21</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.56</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.25</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.58</v>
-      </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.85</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.21</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.56</v>
+        <v>1.94</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2096,13 +2096,13 @@
         <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.38</v>
+        <v>3.01</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.38</v>
@@ -2123,10 +2123,10 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>
@@ -2141,13 +2141,13 @@
         <v>3.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
         <v>2.25</v>
@@ -1745,7 +1745,7 @@
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.8</v>
+        <v>4.11</v>
       </c>
       <c r="R11" t="n">
         <v>1.38</v>
@@ -1766,7 +1766,7 @@
         <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
         <v>1.33</v>
@@ -1775,10 +1775,10 @@
         <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
         <v>3.4</v>
@@ -1787,16 +1787,16 @@
         <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.94</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1852,19 +1852,19 @@
         <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="P12" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
         <v>1.31</v>
@@ -1873,7 +1873,7 @@
         <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.58</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
         <v>1.44</v>
@@ -1888,16 +1888,16 @@
         <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
         <v>3.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
         <v>2.74</v>
@@ -1906,13 +1906,13 @@
         <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
         <v>1.65</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.11</v>
+        <v>3.68</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="O12" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.68</v>
+        <v>4.11</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>4.1</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.68</v>
+        <v>4.11</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>2.45</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>6.1</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.74</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.21</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.1</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>2.77</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.11</v>
+        <v>3.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>3.02</v>
       </c>
       <c r="T12" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>2.74</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>2.21</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.13</v>
+        <v>2.71</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.55</v>
       </c>
       <c r="O14" t="n">
-        <v>3.01</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
         <v>2.2</v>
@@ -2111,7 +2111,7 @@
         <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.37</v>
@@ -2132,13 +2132,13 @@
         <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.27</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
@@ -2147,7 +2147,7 @@
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.11</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.71</v>
+        <v>3.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.55</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
         <v>3.1</v>
@@ -2111,7 +2111,7 @@
         <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="U14" t="n">
         <v>1.37</v>
@@ -2123,22 +2123,22 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
@@ -2147,7 +2147,7 @@
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
         <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.25</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2117,7 +2117,7 @@
         <v>1.37</v>
       </c>
       <c r="V14" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="W14" t="n">
         <v>1.03</v>
@@ -2126,7 +2126,7 @@
         <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI14"/>
+  <dimension ref="A1:V14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,90 +523,25 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Over25</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>HT_Odd_Under25</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>FT_Odd_Over05</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over15</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under15</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over25</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under25</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Over35</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_Under35</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_Yes</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_BTTS_No</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_H_D</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_A_D</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -688,46 +623,7 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" s="3" t="n">
+      <c r="V2" s="3" t="n">
         <v>46009.29166666666</v>
       </c>
     </row>
@@ -807,46 +703,7 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" s="3" t="n">
+      <c r="V3" s="3" t="n">
         <v>46009.40625</v>
       </c>
     </row>
@@ -926,46 +783,7 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="V4" s="3" t="n">
         <v>46009.45486111111</v>
       </c>
     </row>
@@ -1045,46 +863,7 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" s="3" t="n">
+      <c r="V5" s="3" t="n">
         <v>46009.47569444445</v>
       </c>
     </row>
@@ -1153,10 +932,10 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1164,46 +943,7 @@
       <c r="U6" t="n">
         <v>0</v>
       </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" s="3" t="n">
+      <c r="V6" s="3" t="n">
         <v>46009.51041666666</v>
       </c>
     </row>
@@ -1283,46 +1023,7 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="3" t="n">
+      <c r="V7" s="3" t="n">
         <v>46009.51041666666</v>
       </c>
     </row>
@@ -1391,57 +1092,18 @@
         <v>2.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>1.75</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V8" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AI8" s="3" t="n">
+      <c r="V8" s="3" t="n">
         <v>46009.52083333334</v>
       </c>
     </row>
@@ -1521,46 +1183,7 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="3" t="n">
+      <c r="V9" s="3" t="n">
         <v>46009.54166666666</v>
       </c>
     </row>
@@ -1640,46 +1263,7 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" s="3" t="n">
+      <c r="V10" s="3" t="n">
         <v>46009.54166666666</v>
       </c>
     </row>
@@ -1759,46 +1343,7 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="3" t="n">
+      <c r="V11" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -1867,57 +1412,18 @@
         <v>4.8</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>1.92</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>1.78</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF12" t="n">
         <v>1.91</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AI12" s="3" t="n">
+      <c r="V12" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -1986,57 +1492,18 @@
         <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>1.7</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>2.02</v>
       </c>
       <c r="T13" t="n">
-        <v>2.58</v>
+        <v>1.57</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AF13" t="n">
         <v>2.25</v>
       </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI13" s="3" t="n">
+      <c r="V13" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -2105,57 +1572,18 @@
         <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.97</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>1.73</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>1.73</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V14" t="n">
-        <v>7</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI14" s="3" t="n">
+      <c r="V14" s="3" t="n">
         <v>46009.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V14"/>
+  <dimension ref="A1:AI14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,25 +523,90 @@
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
+          <t>HT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under05</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over15</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under15</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Over25</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>HT_Odd_Under25</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>FT_Odd_Over05</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over15</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under15</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
           <t>Odd_Over25</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Odd_Under25</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Over35</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_Under35</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_Yes</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>Odd_BTTS_No</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_H_D</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_A_D</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -623,7 +688,46 @@
       <c r="U2" t="n">
         <v>0</v>
       </c>
-      <c r="V2" s="3" t="n">
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" s="3" t="n">
         <v>46009.29166666666</v>
       </c>
     </row>
@@ -703,7 +807,46 @@
       <c r="U3" t="n">
         <v>0</v>
       </c>
-      <c r="V3" s="3" t="n">
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
       </c>
     </row>
@@ -783,7 +926,46 @@
       <c r="U4" t="n">
         <v>0</v>
       </c>
-      <c r="V4" s="3" t="n">
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
         <v>46009.45486111111</v>
       </c>
     </row>
@@ -863,7 +1045,46 @@
       <c r="U5" t="n">
         <v>0</v>
       </c>
-      <c r="V5" s="3" t="n">
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
       </c>
     </row>
@@ -932,18 +1153,57 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>2.14</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AB6" t="n">
         <v>1.52</v>
       </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="3" t="n">
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
       </c>
     </row>
@@ -1023,7 +1283,46 @@
       <c r="U7" t="n">
         <v>0</v>
       </c>
-      <c r="V7" s="3" t="n">
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
       </c>
     </row>
@@ -1092,18 +1391,57 @@
         <v>2.3</v>
       </c>
       <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V8" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="n">
         <v>1.8</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AB8" t="n">
         <v>1.85</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AC8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.75</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AF8" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="3" t="n">
+      <c r="AG8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
       </c>
     </row>
@@ -1183,7 +1521,46 @@
       <c r="U9" t="n">
         <v>0</v>
       </c>
-      <c r="V9" s="3" t="n">
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
       </c>
     </row>
@@ -1263,7 +1640,46 @@
       <c r="U10" t="n">
         <v>0</v>
       </c>
-      <c r="V10" s="3" t="n">
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
       </c>
     </row>
@@ -1343,7 +1759,46 @@
       <c r="U11" t="n">
         <v>0</v>
       </c>
-      <c r="V11" s="3" t="n">
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -1412,18 +1867,57 @@
         <v>4.8</v>
       </c>
       <c r="R12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.92</v>
       </c>
-      <c r="S12" t="n">
+      <c r="AB12" t="n">
         <v>1.78</v>
       </c>
-      <c r="T12" t="n">
+      <c r="AC12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.83</v>
       </c>
-      <c r="U12" t="n">
+      <c r="AF12" t="n">
         <v>1.91</v>
       </c>
-      <c r="V12" s="3" t="n">
+      <c r="AG12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -1492,18 +1986,57 @@
         <v>3.5</v>
       </c>
       <c r="R13" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.7</v>
       </c>
-      <c r="S13" t="n">
+      <c r="AB13" t="n">
         <v>2.02</v>
       </c>
-      <c r="T13" t="n">
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.57</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AF13" t="n">
         <v>2.25</v>
       </c>
-      <c r="V13" s="3" t="n">
+      <c r="AG13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
       </c>
     </row>
@@ -1572,18 +2105,57 @@
         <v>3.1</v>
       </c>
       <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="n">
         <v>1.97</v>
       </c>
-      <c r="S14" t="n">
+      <c r="AB14" t="n">
         <v>1.73</v>
       </c>
-      <c r="T14" t="n">
+      <c r="AC14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.73</v>
       </c>
-      <c r="U14" t="n">
+      <c r="AF14" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="3" t="n">
+      <c r="AG14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>
       </c>
     </row>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>2.85</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.52</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
         <v>1.28</v>
@@ -1995,7 +1995,7 @@
         <v>2.58</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="V13" t="n">
         <v>6.15</v>
@@ -2096,13 +2096,13 @@
         <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.38</v>
       </c>
       <c r="P14" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
       <c r="R14" t="n">
         <v>1.38</v>
@@ -2123,7 +2123,7 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.26</v>
@@ -2138,7 +2138,7 @@
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>9.1</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>4.75</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46009.29166666666</v>
@@ -784,7 +784,7 @@
         <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>4.42</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.78</v>
+        <v>2.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>4.54</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.45</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.65</v>
+        <v>1.9</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>2.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.9</v>
+        <v>1.65</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -2087,25 +2087,25 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.13</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.2</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="O14" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.19</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S14" t="n">
         <v>2.81</v>
@@ -2123,7 +2123,7 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="n">
         <v>1.26</v>
@@ -2132,10 +2132,10 @@
         <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC14" t="n">
         <v>3.7</v>
@@ -2147,7 +2147,7 @@
         <v>1.73</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -784,7 +784,7 @@
         <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -823,10 +823,10 @@
         <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.48</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.9</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.45</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.79</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.54</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>2.25</v>
@@ -1775,10 +1775,10 @@
         <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
         <v>3.4</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V11" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>6.15</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>3.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.2</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.45</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P14" t="n">
         <v>2.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="R14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="V14" t="n">
         <v>7</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
         <v>3.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.32</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.1</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="O2" t="n">
         <v>8</v>
@@ -677,10 +677,10 @@
         <v>1.73</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.08</v>
+        <v>3.3</v>
       </c>
       <c r="T2" t="n">
         <v>2.34</v>
@@ -689,10 +689,10 @@
         <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="W2" t="n">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -704,13 +704,13 @@
         <v>4.4</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
@@ -722,10 +722,10 @@
         <v>1.75</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46009.29166666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -787,40 +787,40 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>5.31</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA3" t="n">
         <v>2.1</v>
@@ -829,22 +829,22 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
@@ -1025,13 +1025,13 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.46</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1052,13 +1052,13 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AA5" t="n">
         <v>2.15</v>
@@ -1067,22 +1067,22 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
@@ -1263,40 +1263,40 @@
         <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA7" t="n">
         <v>1.85</v>
@@ -1305,22 +1305,22 @@
         <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1373,61 +1373,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>4.51</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O8" t="n">
         <v>3.6</v>
       </c>
-      <c r="N8" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="O8" t="n">
-        <v>5.21</v>
-      </c>
       <c r="P8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
         <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="T8" t="n">
-        <v>2.65</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.29</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
         <v>1.75</v>
@@ -1436,10 +1436,10 @@
         <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.95</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1739,22 +1739,22 @@
         <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="R11" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="T11" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
         <v>1.44</v>
@@ -1772,7 +1772,7 @@
         <v>1.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="AA11" t="n">
         <v>1.7</v>
@@ -1784,16 +1784,16 @@
         <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH11" t="n">
         <v>1.65</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>5.21</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="P13" t="n">
         <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.8</v>
+        <v>9.25</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>2.93</v>
+        <v>3.1</v>
       </c>
       <c r="U13" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>6.55</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>2.85</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2096,13 +2096,13 @@
         <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P14" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
@@ -2114,13 +2114,13 @@
         <v>2.86</v>
       </c>
       <c r="U14" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="V14" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
         <v>1</v>
@@ -2129,7 +2129,7 @@
         <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA14" t="n">
         <v>1.97</v>
@@ -2141,7 +2141,7 @@
         <v>3.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
         <v>1.75</v>
@@ -2150,10 +2150,10 @@
         <v>2</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="O7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.23</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,34 +1492,34 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>3.99</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>2.09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.02</v>
+        <v>5.42</v>
       </c>
       <c r="P9" t="n">
-        <v>1.84</v>
+        <v>1.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.55</v>
+        <v>2.81</v>
       </c>
       <c r="R9" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.23</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="V9" t="n">
         <v>9.699999999999999</v>
@@ -1528,37 +1528,37 @@
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.6</v>
+        <v>5.55</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.49</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,34 +1611,34 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.99</v>
+        <v>2.58</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>2.83</v>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>2.78</v>
       </c>
       <c r="O10" t="n">
-        <v>5.42</v>
+        <v>3.02</v>
       </c>
       <c r="P10" t="n">
-        <v>1.77</v>
+        <v>1.84</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.81</v>
+        <v>4.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2.23</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="U10" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="V10" t="n">
         <v>9.699999999999999</v>
@@ -1647,37 +1647,37 @@
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.16</v>
+        <v>1.49</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="P11" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.62</v>
+        <v>9.25</v>
       </c>
       <c r="R11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U11" t="n">
         <v>1.33</v>
       </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.44</v>
-      </c>
       <c r="V11" t="n">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.8</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>2.6</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.25</v>
+        <v>1.45</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.65</v>
+        <v>2.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>9.25</v>
+        <v>3.62</v>
       </c>
       <c r="R13" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V13" t="n">
-        <v>7.5</v>
+        <v>6.15</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="AB13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.6</v>
       </c>
-      <c r="AC13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.6</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.45</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.85</v>
+        <v>1.65</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -674,13 +674,13 @@
         <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
         <v>2.34</v>
@@ -689,10 +689,10 @@
         <v>1.49</v>
       </c>
       <c r="V2" t="n">
-        <v>5.2</v>
+        <v>5.15</v>
       </c>
       <c r="W2" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="X2" t="n">
         <v>1.03</v>
@@ -701,7 +701,7 @@
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
         <v>1.65</v>
@@ -710,22 +710,22 @@
         <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
         <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>2.07</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.11</v>
+        <v>1.17</v>
       </c>
       <c r="AH2" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46009.29166666666</v>
@@ -787,13 +787,13 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="P3" t="n">
         <v>2.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.31</v>
+        <v>5.26</v>
       </c>
       <c r="R3" t="n">
         <v>1.43</v>
@@ -802,10 +802,10 @@
         <v>2.5</v>
       </c>
       <c r="T3" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="U3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>6.9</v>
@@ -820,7 +820,7 @@
         <v>1.33</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AA3" t="n">
         <v>2.1</v>
@@ -829,22 +829,22 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.58</v>
+        <v>3.68</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AG3" t="n">
         <v>1.24</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
@@ -1025,40 +1025,40 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="P5" t="n">
         <v>2.05</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.46</v>
+        <v>4.39</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AA5" t="n">
         <v>2.15</v>
@@ -1067,22 +1067,22 @@
         <v>1.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>2.07</v>
+        <v>3.42</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.23</v>
+        <v>3.22</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.46</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.34</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.85</v>
+        <v>2.17</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.85</v>
+        <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.62</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>6.23</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1394,25 +1394,25 @@
         <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.71</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V8" t="n">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="W8" t="n">
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
         <v>3.3</v>
@@ -1424,16 +1424,16 @@
         <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="AG8" t="n">
         <v>1.33</v>
@@ -1513,7 +1513,7 @@
         <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="T9" t="n">
         <v>3.9</v>
@@ -1537,10 +1537,10 @@
         <v>2.1</v>
       </c>
       <c r="AA9" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
         <v>5.55</v>
@@ -1635,7 +1635,7 @@
         <v>2.23</v>
       </c>
       <c r="T10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>1.22</v>
@@ -1656,7 +1656,7 @@
         <v>2.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.02</v>
+        <v>2.89</v>
       </c>
       <c r="AB10" t="n">
         <v>1.36</v>
@@ -1677,7 +1677,7 @@
         <v>1.49</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
         <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.25</v>
+        <v>5.27</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V11" t="n">
         <v>7.5</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.2</v>
+        <v>3.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.6</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.45</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.85</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH12" t="n">
         <v>1.65</v>
-      </c>
-      <c r="M12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,37 +1968,37 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.62</v>
+        <v>7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.48</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>6.15</v>
+        <v>7.5</v>
       </c>
       <c r="W13" t="n">
         <v>1.06</v>
@@ -2007,34 +2007,34 @@
         <v>1.04</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.8</v>
+        <v>2.66</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
-        <v>2.9</v>
+        <v>3.86</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.34</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>2.48</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.65</v>
+        <v>2.53</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2108,7 +2108,7 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>2.98</v>
       </c>
       <c r="T14" t="n">
         <v>2.86</v>
@@ -2138,16 +2138,16 @@
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.32</v>
+        <v>3.65</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AG14" t="n">
         <v>1.28</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -659,37 +659,37 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>9.9</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>9.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.34</v>
+        <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>1.49</v>
+        <v>1.59</v>
       </c>
       <c r="V2" t="n">
-        <v>5.15</v>
+        <v>5.05</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -704,22 +704,22 @@
         <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.07</v>
+        <v>1.95</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AG2" t="n">
         <v>1.17</v>
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>3.96</v>
       </c>
       <c r="O3" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="P3" t="n">
-        <v>2.01</v>
+        <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>5.26</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="S3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="T3" t="n">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="V3" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
       <c r="W3" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.07</v>
       </c>
-      <c r="X3" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y3" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.81</v>
+        <v>2.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH3" t="n">
         <v>1.74</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.87</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
@@ -1016,28 +1016,28 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="M5" t="n">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="N5" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>2.05</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="R5" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="T5" t="n">
         <v>3.04</v>
@@ -1061,13 +1061,13 @@
         <v>2.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.76</v>
+        <v>3.95</v>
       </c>
       <c r="AD5" t="n">
         <v>1.19</v>
@@ -1079,7 +1079,7 @@
         <v>1.77</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH5" t="n">
         <v>1.65</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.78</v>
+        <v>1.49</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>6.1</v>
       </c>
       <c r="O6" t="n">
-        <v>3.42</v>
+        <v>2.08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.22</v>
+        <v>6.23</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.46</v>
+        <v>2.75</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U6" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V6" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>1.9</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.84</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AF6" t="n">
         <v>1.8</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>2.72</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.04</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>2.41</v>
       </c>
       <c r="O7" t="n">
-        <v>2.08</v>
+        <v>3.48</v>
       </c>
       <c r="P7" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.23</v>
+        <v>3.18</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.34</v>
+        <v>2.74</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.58</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.15</v>
       </c>
       <c r="N8" t="n">
         <v>2.25</v>
@@ -1391,16 +1391,16 @@
         <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.8</v>
+        <v>2.67</v>
       </c>
       <c r="T8" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="U8" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>6.7</v>
@@ -1409,7 +1409,7 @@
         <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
         <v>1.3</v>
@@ -1418,28 +1418,28 @@
         <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>3.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="M9" t="n">
-        <v>2.7</v>
+        <v>2.87</v>
       </c>
       <c r="N9" t="n">
-        <v>2.09</v>
+        <v>1.96</v>
       </c>
       <c r="O9" t="n">
-        <v>5.42</v>
+        <v>5.53</v>
       </c>
       <c r="P9" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="R9" t="n">
         <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="U9" t="n">
         <v>1.18</v>
@@ -1534,31 +1534,31 @@
         <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.89</v>
+        <v>2.81</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.55</v>
+        <v>5.65</v>
       </c>
       <c r="AD9" t="n">
         <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG9" t="n">
         <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1611,37 +1611,37 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.58</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.55</v>
+        <v>4.33</v>
       </c>
       <c r="R10" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2.23</v>
+        <v>2.07</v>
       </c>
       <c r="T10" t="n">
         <v>4</v>
       </c>
       <c r="U10" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
@@ -1650,31 +1650,31 @@
         <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="AF10" t="n">
         <v>1.53</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
         <v>1.53</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.27</v>
+        <v>8.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>2.38</v>
       </c>
       <c r="T11" t="n">
-        <v>2.7</v>
+        <v>3.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>7.5</v>
+        <v>9</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.92</v>
+        <v>2.19</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1849,16 +1849,16 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N12" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.73</v>
+        <v>2.69</v>
       </c>
       <c r="P12" t="n">
         <v>2.33</v>
@@ -1891,31 +1891,31 @@
         <v>1.22</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
         <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>7.9</v>
+        <v>4.47</v>
       </c>
       <c r="O13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.98</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.86</v>
+        <v>3.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.48</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.48</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.53</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.49</v>
+        <v>2.72</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>3.04</v>
       </c>
       <c r="N6" t="n">
-        <v>6.1</v>
+        <v>2.41</v>
       </c>
       <c r="O6" t="n">
-        <v>2.08</v>
+        <v>3.48</v>
       </c>
       <c r="P6" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>6.23</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.75</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.71</v>
+        <v>3.2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.37</v>
+        <v>1.27</v>
       </c>
       <c r="V6" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.3</v>
+        <v>2.74</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.84</v>
+        <v>1.58</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.05</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.18</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.72</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>3.04</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>2.41</v>
+        <v>6.1</v>
       </c>
       <c r="O7" t="n">
-        <v>3.48</v>
+        <v>2.08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92</v>
+        <v>2.13</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.18</v>
+        <v>6.23</v>
       </c>
       <c r="R7" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>2.47</v>
+        <v>2.75</v>
       </c>
       <c r="T7" t="n">
-        <v>3.2</v>
+        <v>2.71</v>
       </c>
       <c r="U7" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="V7" t="n">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.74</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.58</v>
+        <v>1.84</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.1</v>
+        <v>3.05</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.35</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="M12" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>3</v>
+        <v>4.47</v>
       </c>
       <c r="O12" t="n">
-        <v>2.69</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.76</v>
+        <v>5.21</v>
       </c>
       <c r="R12" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.05</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.75</v>
+        <v>3.36</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.26</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.55</v>
+        <v>1.92</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.25</v>
+        <v>1.82</v>
       </c>
       <c r="AG12" t="n">
         <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M13" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.7</v>
       </c>
-      <c r="M13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
+      <c r="AB13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.75</v>
       </c>
-      <c r="U13" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.36</v>
-      </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>1.55</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AG13" t="n">
         <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.13</v>
+        <v>2.68</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.32</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.46</v>
       </c>
       <c r="O14" t="n">
         <v>3.1</v>
@@ -2108,10 +2108,10 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.98</v>
+        <v>2.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2123,7 +2123,7 @@
         <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="Y14" t="n">
         <v>1.33</v>
@@ -2132,13 +2132,13 @@
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
@@ -2150,7 +2150,7 @@
         <v>2.02</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
         <v>1.44</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -778,58 +778,58 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.73</v>
       </c>
       <c r="M3" t="n">
-        <v>3.12</v>
+        <v>3.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.96</v>
+        <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="Q3" t="n">
         <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="U3" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="V3" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="W3" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
         <v>2.74</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AD3" t="n">
         <v>1.19</v>
@@ -841,10 +841,10 @@
         <v>1.75</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="M5" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="N5" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>2.93</v>
       </c>
       <c r="P5" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V5" t="n">
+        <v>11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2.01</v>
       </c>
-      <c r="Q5" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="T5" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V5" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X5" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AF5" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.48</v>
+        <v>3.84</v>
       </c>
       <c r="P6" t="n">
         <v>1.92</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.18</v>
+        <v>2.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
       <c r="U6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V6" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.27</v>
       </c>
-      <c r="V6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH6" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="P7" t="n">
         <v>2.08</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.13</v>
-      </c>
       <c r="Q7" t="n">
-        <v>6.23</v>
+        <v>6.62</v>
       </c>
       <c r="R7" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T7" t="n">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="U7" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="V7" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4</v>
+        <v>2.58</v>
       </c>
       <c r="M9" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="N9" t="n">
-        <v>1.96</v>
+        <v>2.78</v>
       </c>
       <c r="O9" t="n">
-        <v>5.53</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.76</v>
+        <v>4.33</v>
       </c>
       <c r="R9" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="S9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="U9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>9.699999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.53</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>3.99</v>
       </c>
       <c r="M10" t="n">
         <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>3.1</v>
+        <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>5.58</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="Q10" t="n">
-        <v>4.33</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S10" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="U10" t="n">
         <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.75</v>
+        <v>6.1</v>
       </c>
       <c r="AD10" t="n">
         <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.27</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.53</v>
+        <v>1.19</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.15</v>
+        <v>5.21</v>
       </c>
       <c r="R11" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S11" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="T11" t="n">
-        <v>3.18</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="V11" t="n">
-        <v>9</v>
+        <v>6.55</v>
       </c>
       <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.8</v>
+        <v>3.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.19</v>
+        <v>1.92</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N12" t="n">
-        <v>4.47</v>
+        <v>7.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V12" t="n">
+        <v>8</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
+      <c r="AB12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
         <v>2.69</v>
@@ -2016,7 +2016,7 @@
         <v>1.7</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AC13" t="n">
         <v>2.75</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9.9</v>
+        <v>7.2</v>
       </c>
       <c r="M2" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="N2" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="O2" t="n">
         <v>9.5</v>
@@ -674,19 +674,19 @@
         <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="R2" t="n">
         <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.2</v>
+        <v>3.14</v>
       </c>
       <c r="T2" t="n">
         <v>2.29</v>
       </c>
       <c r="U2" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="V2" t="n">
         <v>5.05</v>
@@ -695,25 +695,25 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="AE2" t="n">
         <v>1.95</v>
@@ -1373,10 +1373,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="M8" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="N8" t="n">
         <v>2.25</v>
@@ -1394,22 +1394,22 @@
         <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="T8" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V8" t="n">
-        <v>6.7</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
         <v>1.3</v>
@@ -1418,28 +1418,28 @@
         <v>3.3</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>1.91</v>
+        <v>2.69</v>
       </c>
       <c r="P12" t="n">
-        <v>2.15</v>
+        <v>2.33</v>
       </c>
       <c r="Q12" t="n">
-        <v>8</v>
+        <v>3.76</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.4</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V12" t="n">
-        <v>8</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.58</v>
+        <v>2.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.75</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.37</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
-        <v>2.69</v>
+        <v>1.91</v>
       </c>
       <c r="P13" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.76</v>
+        <v>8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.5</v>
+        <v>2.83</v>
       </c>
       <c r="U13" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="X13" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>4</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.02</v>
+        <v>1.6</v>
       </c>
       <c r="AC13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2.75</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.68</v>
+        <v>3.13</v>
       </c>
       <c r="M14" t="n">
-        <v>3.32</v>
+        <v>3.13</v>
       </c>
       <c r="N14" t="n">
-        <v>2.46</v>
+        <v>2.08</v>
       </c>
       <c r="O14" t="n">
         <v>3.1</v>
@@ -2108,7 +2108,7 @@
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="T14" t="n">
         <v>2.87</v>
@@ -2126,16 +2126,16 @@
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AC14" t="n">
         <v>3.7</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -674,19 +674,19 @@
         <v>2.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>3.14</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="V2" t="n">
         <v>5.05</v>
@@ -695,10 +695,10 @@
         <v>1.1</v>
       </c>
       <c r="X2" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z2" t="n">
         <v>4.25</v>
@@ -713,10 +713,10 @@
         <v>2.35</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>1.75</v>
@@ -787,13 +787,13 @@
         <v>4.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="P3" t="n">
         <v>1.97</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>4.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
@@ -802,10 +802,10 @@
         <v>2.47</v>
       </c>
       <c r="T3" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="U3" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V3" t="n">
         <v>7</v>
@@ -820,7 +820,7 @@
         <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="AA3" t="n">
         <v>2.1</v>
@@ -829,13 +829,13 @@
         <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AF3" t="n">
         <v>1.75</v>
@@ -1025,40 +1025,40 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="P5" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S5" t="n">
         <v>2.28</v>
       </c>
       <c r="T5" t="n">
-        <v>3.34</v>
+        <v>3.4</v>
       </c>
       <c r="U5" t="n">
         <v>1.24</v>
       </c>
       <c r="V5" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="W5" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X5" t="n">
         <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AA5" t="n">
         <v>2.15</v>
@@ -1076,13 +1076,13 @@
         <v>2.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG5" t="n">
         <v>1.31</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
@@ -1144,22 +1144,22 @@
         <v>2.28</v>
       </c>
       <c r="O6" t="n">
-        <v>3.84</v>
+        <v>3.55</v>
       </c>
       <c r="P6" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
         <v>2.97</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.53</v>
       </c>
       <c r="T6" t="n">
-        <v>3.12</v>
+        <v>2.86</v>
       </c>
       <c r="U6" t="n">
         <v>1.28</v>
@@ -1174,10 +1174,10 @@
         <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.83</v>
+        <v>3.06</v>
       </c>
       <c r="AA6" t="n">
         <v>2.17</v>
@@ -1186,10 +1186,10 @@
         <v>1.61</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
         <v>1.83</v>
@@ -1263,22 +1263,22 @@
         <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
         <v>2.08</v>
       </c>
       <c r="Q7" t="n">
-        <v>6.62</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S7" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="U7" t="n">
         <v>1.34</v>
@@ -1311,13 +1311,13 @@
         <v>1.26</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.77</v>
+        <v>1.68</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.05</v>
+        <v>1.19</v>
       </c>
       <c r="AH7" t="n">
         <v>2.32</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.65</v>
+        <v>1.37</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>7.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>5.21</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="AB11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH11" t="n">
         <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.55</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.05</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.37</v>
+        <v>1.65</v>
       </c>
       <c r="M13" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>7.9</v>
+        <v>4.5</v>
       </c>
       <c r="O13" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>5.21</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V13" t="n">
-        <v>8</v>
+        <v>6.55</v>
       </c>
       <c r="W13" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.97</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.2</v>
+        <v>1.92</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.33</v>
+        <v>3.36</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.32</v>
+        <v>1.92</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1382,40 +1382,40 @@
         <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.6</v>
+        <v>3.62</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.75</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.81</v>
-      </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="V8" t="n">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
         <v>1.3</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.3</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
         <v>1.95</v>
@@ -1424,7 +1424,7 @@
         <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AD8" t="n">
         <v>1.25</v>
@@ -1433,13 +1433,13 @@
         <v>1.79</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.99</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.53</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
@@ -1507,19 +1507,19 @@
         <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="S9" t="n">
         <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="U9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="V9" t="n">
         <v>9.4</v>
@@ -1528,7 +1528,7 @@
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
         <v>1.6</v>
@@ -1546,7 +1546,7 @@
         <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
         <v>2.38</v>
@@ -1558,7 +1558,7 @@
         <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1620,13 +1620,13 @@
         <v>2.09</v>
       </c>
       <c r="O10" t="n">
-        <v>5.58</v>
+        <v>5</v>
       </c>
       <c r="P10" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>2.7</v>
       </c>
       <c r="R10" t="n">
         <v>1.65</v>
@@ -1635,7 +1635,7 @@
         <v>2.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="U10" t="n">
         <v>1.17</v>
@@ -1662,22 +1662,22 @@
         <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>6.1</v>
+        <v>5.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.37</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>7.9</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.91</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q11" t="n">
-        <v>8</v>
+        <v>3.45</v>
       </c>
       <c r="R11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V11" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.4</v>
       </c>
-      <c r="S11" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V11" t="n">
-        <v>8</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.32</v>
+        <v>1.55</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.58</v>
+        <v>2.23</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.75</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.1</v>
+        <v>1.65</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S12" t="n">
         <v>2.9</v>
       </c>
-      <c r="O12" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="V12" t="n">
-        <v>6</v>
+        <v>6.55</v>
       </c>
       <c r="W12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.06</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AB12" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH12" t="n">
         <v>2.02</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.21</v>
+        <v>8.27</v>
       </c>
       <c r="R13" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
         <v>2.7</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>2.91</v>
       </c>
       <c r="U13" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V13" t="n">
-        <v>6.55</v>
+        <v>7.1</v>
       </c>
       <c r="W13" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>2.96</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.92</v>
+        <v>2.25</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.78</v>
+        <v>1.57</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.36</v>
+        <v>4.33</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.92</v>
+        <v>2.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.05</v>
+        <v>2.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2102,16 +2102,16 @@
         <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>1.39</v>
       </c>
       <c r="S14" t="n">
-        <v>2.77</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="U14" t="n">
         <v>1.36</v>
@@ -2126,7 +2126,7 @@
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
@@ -2138,13 +2138,13 @@
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AF14" t="n">
         <v>2.02</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -642,54 +642,54 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="M2" t="n">
-        <v>4.6</v>
+        <v>4.55</v>
       </c>
       <c r="N2" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="O2" t="n">
-        <v>9.5</v>
+        <v>7</v>
       </c>
       <c r="P2" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S2" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="T2" t="n">
         <v>2.3</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="V2" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="W2" t="n">
         <v>1.1</v>
@@ -698,25 +698,25 @@
         <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.15</v>
+        <v>1.18</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.25</v>
+        <v>4.5</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AB2" t="n">
         <v>2.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.35</v>
+        <v>2.42</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF2" t="n">
         <v>1.75</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="O6" t="n">
-        <v>3.55</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S6" t="n">
-        <v>2.53</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V6" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="W6" t="n">
         <v>1.08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.31</v>
+        <v>2.32</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="O7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="P7" t="n">
         <v>2</v>
       </c>
-      <c r="P7" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2.97</v>
       </c>
       <c r="R7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>2.53</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG7" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="O11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.27</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V11" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE11" t="n">
         <v>2.5</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U11" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V11" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF11" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="O13" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.27</v>
+        <v>3.45</v>
       </c>
       <c r="R13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC13" t="n">
         <v>2.7</v>
       </c>
-      <c r="T13" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V13" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
+      <c r="AD13" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AH13" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -778,73 +778,73 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.73</v>
+        <v>2.25</v>
       </c>
       <c r="M3" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N3" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P3" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.99</v>
+        <v>4.4</v>
       </c>
       <c r="R3" t="n">
         <v>1.44</v>
       </c>
       <c r="S3" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="T3" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.78</v>
+        <v>2.56</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46009.40625</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>7.75</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46009.45486111111</v>
@@ -1025,7 +1025,7 @@
         <v>3.05</v>
       </c>
       <c r="O5" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
         <v>2</v>
@@ -1034,16 +1034,16 @@
         <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="T5" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="U5" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="V5" t="n">
         <v>8.6</v>
@@ -1052,7 +1052,7 @@
         <v>1.04</v>
       </c>
       <c r="X5" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y5" t="n">
         <v>1.44</v>
@@ -1070,19 +1070,19 @@
         <v>4.75</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>2.01</v>
+        <v>2.06</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46009.47569444445</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.45</v>
+        <v>2.78</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>3.11</v>
       </c>
       <c r="N6" t="n">
-        <v>6.2</v>
+        <v>2.28</v>
       </c>
       <c r="O6" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="P6" t="n">
         <v>2</v>
       </c>
-      <c r="P6" t="n">
-        <v>2.08</v>
-      </c>
       <c r="Q6" t="n">
-        <v>5</v>
+        <v>2.76</v>
       </c>
       <c r="R6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="U6" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG6" t="n">
         <v>1.27</v>
       </c>
-      <c r="Z6" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AH6" t="n">
-        <v>2.32</v>
+        <v>1.24</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,37 +1254,37 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.78</v>
+        <v>1.45</v>
       </c>
       <c r="M7" t="n">
-        <v>3.11</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>2.28</v>
+        <v>6.2</v>
       </c>
       <c r="O7" t="n">
-        <v>3.55</v>
+        <v>2</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.97</v>
+        <v>5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="W7" t="n">
         <v>1.08</v>
@@ -1293,34 +1293,34 @@
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.06</v>
+        <v>3.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.61</v>
+        <v>1.85</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.95</v>
+        <v>3.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>2.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.31</v>
+        <v>2.27</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1382,40 +1382,40 @@
         <v>2.25</v>
       </c>
       <c r="O8" t="n">
-        <v>3.62</v>
+        <v>3.58</v>
       </c>
       <c r="P8" t="n">
-        <v>2.05</v>
+        <v>2.14</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>3.42</v>
       </c>
       <c r="AA8" t="n">
         <v>1.95</v>
@@ -1424,22 +1424,22 @@
         <v>1.75</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46009.52083333334</v>
@@ -1516,19 +1516,19 @@
         <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="U9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
         <v>1.6</v>
@@ -1546,7 +1546,7 @@
         <v>5.75</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
         <v>2.38</v>
@@ -1558,7 +1558,7 @@
         <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1626,7 +1626,7 @@
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="R10" t="n">
         <v>1.65</v>
@@ -1647,7 +1647,7 @@
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y10" t="n">
         <v>1.65</v>
@@ -1668,10 +1668,10 @@
         <v>1.07</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="AG10" t="n">
         <v>1.32</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="M11" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>7</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.27</v>
+        <v>3.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S11" t="n">
-        <v>2.7</v>
+        <v>3.32</v>
       </c>
       <c r="T11" t="n">
-        <v>2.91</v>
+        <v>2.5</v>
       </c>
       <c r="U11" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="V11" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="W11" t="n">
         <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.32</v>
+        <v>1.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.25</v>
+        <v>1.7</v>
       </c>
       <c r="AB11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH11" t="n">
         <v>1.57</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>2.8</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1861,7 +1861,7 @@
         <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q12" t="n">
         <v>5.21</v>
@@ -1870,7 +1870,7 @@
         <v>1.36</v>
       </c>
       <c r="S12" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="T12" t="n">
         <v>2.7</v>
@@ -1891,7 +1891,7 @@
         <v>1.28</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
         <v>1.92</v>
@@ -1903,13 +1903,13 @@
         <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
         <v>1.83</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG12" t="n">
         <v>1.25</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="N13" t="n">
-        <v>2.9</v>
+        <v>7</v>
       </c>
       <c r="O13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2.5</v>
       </c>
-      <c r="P13" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.95</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.55</v>
-      </c>
       <c r="AF13" t="n">
-        <v>2.23</v>
+        <v>1.44</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>2.8</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2096,7 +2096,7 @@
         <v>2.08</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -2105,28 +2105,28 @@
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="T14" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="U14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V14" t="n">
-        <v>7.5</v>
+        <v>7.8</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
         <v>1.06</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
         <v>3.25</v>
@@ -2138,16 +2138,16 @@
         <v>1.73</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
         <v>1.3</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="AG14" t="n">
         <v>1.33</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -761,20 +761,20 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L3" t="n">
@@ -883,17 +883,17 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L4" t="n">
@@ -999,20 +999,20 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L5" t="n">
@@ -1118,39 +1118,39 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.11</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.76</v>
+        <v>2.93</v>
       </c>
       <c r="R6" t="n">
         <v>1.44</v>
@@ -1159,16 +1159,16 @@
         <v>2.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
         <v>1.28</v>
       </c>
       <c r="V6" t="n">
-        <v>6.8</v>
+        <v>7.1</v>
       </c>
       <c r="W6" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
         <v>1.05</v>
@@ -1177,31 +1177,31 @@
         <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
         <v>3.95</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1237,30 +1237,30 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="O7" t="n">
         <v>2</v>
@@ -1278,40 +1278,40 @@
         <v>2.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="U7" t="n">
         <v>1.33</v>
       </c>
       <c r="V7" t="n">
-        <v>6.6</v>
+        <v>8</v>
       </c>
       <c r="W7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X7" t="n">
         <v>1.04</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
         <v>3.04</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AF7" t="n">
         <v>1.66</v>
@@ -1356,57 +1356,57 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="M8" t="n">
-        <v>3.3</v>
+        <v>3.32</v>
       </c>
       <c r="N8" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="O8" t="n">
-        <v>3.58</v>
+        <v>3.78</v>
       </c>
       <c r="P8" t="n">
-        <v>2.14</v>
+        <v>2.04</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="U8" t="n">
         <v>1.36</v>
       </c>
-      <c r="S8" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="V8" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
@@ -1415,28 +1415,28 @@
         <v>1.27</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.42</v>
+        <v>3.14</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC8" t="n">
         <v>3.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AF8" t="n">
         <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="AH8" t="n">
         <v>1.36</v>
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.58</v>
+        <v>2.3</v>
       </c>
       <c r="M9" t="n">
-        <v>2.83</v>
+        <v>2.75</v>
       </c>
       <c r="N9" t="n">
-        <v>2.78</v>
+        <v>3.2</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -1507,7 +1507,7 @@
         <v>1.85</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="R9" t="n">
         <v>1.64</v>
@@ -1522,25 +1522,25 @@
         <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC9" t="n">
         <v>5.75</v>
@@ -1549,16 +1549,16 @@
         <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.53</v>
+        <v>1.47</v>
       </c>
       <c r="AG9" t="n">
         <v>1.44</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.67</v>
+        <v>1.51</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.99</v>
+        <v>4.5</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>2.09</v>
+        <v>1.79</v>
       </c>
       <c r="O10" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="P10" t="n">
         <v>1.83</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.68</v>
+        <v>2.51</v>
       </c>
       <c r="R10" t="n">
         <v>1.65</v>
@@ -1653,31 +1653,31 @@
         <v>1.65</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.89</v>
+        <v>2.97</v>
       </c>
       <c r="AB10" t="n">
         <v>1.36</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.55</v>
+        <v>2.61</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.32</v>
+        <v>2.03</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.6</v>
+        <v>5.12</v>
       </c>
       <c r="R11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>3.32</v>
+        <v>2.59</v>
       </c>
       <c r="T11" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="U11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="V11" t="n">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.06</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.7</v>
+        <v>2.02</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.74</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,22 +1849,22 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="N12" t="n">
-        <v>4.5</v>
+        <v>7.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="P12" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.21</v>
+        <v>7.15</v>
       </c>
       <c r="R12" t="n">
         <v>1.36</v>
@@ -1876,46 +1876,46 @@
         <v>2.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="V12" t="n">
-        <v>6.55</v>
+        <v>6.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>2.8</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.84</v>
+        <v>1.44</v>
       </c>
       <c r="AG12" t="n">
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.02</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="M13" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>3.2</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="P13" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.43</v>
+        <v>3.9</v>
       </c>
       <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD13" t="n">
         <v>1.36</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.8</v>
+        <v>1.75</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>

--- a/jogos_2025-12-18.xlsx
+++ b/jogos_2025-12-18.xlsx
@@ -1109,22 +1109,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Al-Nahda</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
       </c>
-      <c r="H6" t="n">
-        <v>2</v>
-      </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>1</v>
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.9</v>
+        <v>1.52</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>2.25</v>
+        <v>5.8</v>
       </c>
       <c r="O6" t="n">
-        <v>3.7</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.93</v>
+        <v>5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.47</v>
+        <v>2.56</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V6" t="n">
-        <v>7.1</v>
+        <v>8</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X6" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.81</v>
+        <v>3.04</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.23</v>
+        <v>1.86</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.95</v>
+        <v>3.34</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.84</v>
+        <v>1.66</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.28</v>
+        <v>2.27</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1228,22 +1228,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Nahda</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>1</v>
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>2.9</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N7" t="n">
-        <v>5.8</v>
+        <v>2.25</v>
       </c>
       <c r="O7" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>5</v>
+        <v>2.93</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>2.56</v>
+        <v>2.47</v>
       </c>
       <c r="T7" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V7" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y7" t="n">
         <v>1.33</v>
       </c>
-      <c r="V7" t="n">
-        <v>8</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z7" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.86</v>
+        <v>2.23</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.86</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.34</v>
+        <v>3.95</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.66</v>
+        <v>1.84</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.27</v>
+        <v>1.28</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46009.51041666666</v>
@@ -1466,99 +1466,99 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="N9" t="n">
-        <v>3.2</v>
+        <v>1.79</v>
       </c>
       <c r="O9" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="P9" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.4</v>
+        <v>2.51</v>
       </c>
       <c r="R9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="T9" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="U9" t="n">
         <v>1.17</v>
       </c>
       <c r="V9" t="n">
-        <v>9.6</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.44</v>
+        <v>2.03</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.51</v>
+        <v>1.1</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1585,99 +1585,99 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.5</v>
+        <v>2.3</v>
       </c>
       <c r="M10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O10" t="n">
         <v>3</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.5</v>
-      </c>
       <c r="P10" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.51</v>
+        <v>4.4</v>
       </c>
       <c r="R10" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="S10" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="T10" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="U10" t="n">
         <v>1.17</v>
       </c>
       <c r="V10" t="n">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.14</v>
+        <v>2.23</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.61</v>
+        <v>2.41</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="AG10" t="n">
-        <v>2.03</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.1</v>
+        <v>1.51</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46009.54166666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>RFC Liege</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="M12" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="N12" t="n">
-        <v>7.4</v>
+        <v>3.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.92</v>
+        <v>2.4</v>
       </c>
       <c r="P12" t="n">
-        <v>2.25</v>
+        <v>2.37</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.15</v>
+        <v>3.9</v>
       </c>
       <c r="R12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S12" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.36</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AG12" t="n">
         <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>1.75</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46009.66666666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RFC Liege</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.95</v>
+        <v>1.41</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N13" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="O13" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="P13" t="n">
-        <v>2.37</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.9</v>
+        <v>7.15</v>
       </c>
       <c r="R13" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S13" t="n">
-        <v>3.33</v>
+        <v>2.7</v>
       </c>
       <c r="T13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="V13" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE13" t="n">
         <v>2.5</v>
       </c>
-      <c r="U13" t="n">
+      <c r="AF13" t="n">
         <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>6.15</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
         <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.75</v>
+        <v>2.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46009.66666666666</v>
@@ -2087,16 +2087,16 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.13</v>
+        <v>2.63</v>
       </c>
       <c r="M14" t="n">
-        <v>3.13</v>
+        <v>3.22</v>
       </c>
       <c r="N14" t="n">
-        <v>2.08</v>
+        <v>2.65</v>
       </c>
       <c r="O14" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
         <v>2</v>
@@ -2105,55 +2105,55 @@
         <v>3</v>
       </c>
       <c r="R14" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S14" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T14" t="n">
-        <v>3.16</v>
+        <v>2.99</v>
       </c>
       <c r="U14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.35</v>
       </c>
-      <c r="V14" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD14" t="n">
+      <c r="AE14" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.3</v>
       </c>
-      <c r="AE14" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH14" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46009.70833333334</v>
